--- a/tools/importer/reports/import-reagent-product.report.xlsx
+++ b/tools/importer/reports/import-reagent-product.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-27T07:46:04.173Z</t>
+    <t>2026-10-28T04:25:20.528Z</t>
   </si>
   <si>
     <t>Reagents - Beckman Coulter Life Sciences</t>
@@ -64,7 +64,7 @@
     <t>reagents/cell-culture</t>
   </si>
   <si>
-    <t>2026-10-27T07:46:56.521Z</t>
+    <t>2026-10-28T04:25:24.201Z</t>
   </si>
   <si>
     <t>Automated Cell Culture and Clone Ranking Reagents</t>
@@ -79,7 +79,7 @@
     <t>reagents/centrifugation</t>
   </si>
   <si>
-    <t>2026-10-27T07:47:48.322Z</t>
+    <t>2026-10-27T10:39:53.838Z</t>
   </si>
   <si>
     <t>Centrifugation</t>
@@ -94,7 +94,7 @@
     <t>reagents/coulter-flow-cytometry</t>
   </si>
   <si>
-    <t>2026-10-27T07:48:43.100Z</t>
+    <t>2026-10-28T04:25:27.304Z</t>
   </si>
   <si>
     <t>Flow Cytometry Reagents, DuraClone IM</t>
@@ -109,7 +109,7 @@
     <t>reagents/genomic</t>
   </si>
   <si>
-    <t>2026-10-27T07:49:35.305Z</t>
+    <t>2026-10-28T04:25:29.867Z</t>
   </si>
   <si>
     <t>Nucleic Acid Sample Prep, Reagent Kits</t>
@@ -124,7 +124,7 @@
     <t>reagents/particle</t>
   </si>
   <si>
-    <t>2026-10-27T07:50:27.122Z</t>
+    <t>2026-10-28T04:25:32.599Z</t>
   </si>
   <si>
     <t>Particle, Cell Counter &amp; Analyzer Reagents</t>
@@ -145,7 +145,7 @@
     <t>reagent-product</t>
   </si>
   <si>
-    <t>2026-10-27T08:31:50.377Z</t>
+    <t>2026-10-28T04:25:39.960Z</t>
   </si>
   <si>
     <t>Valita Aggregation Pure Assays to determine Protein Aggregation</t>
@@ -163,7 +163,7 @@
     <t>reagents/particle/valita-titer-assays</t>
   </si>
   <si>
-    <t>2026-10-27T08:31:47.747Z</t>
+    <t>2026-10-28T04:25:37.311Z</t>
   </si>
   <si>
     <t>Valita Titer Assays for IgG Quantification</t>
